--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GithubClonefiles\datacentra_unitcommitment\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyiping/Documents/GitHub/module_unitcommitment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F268AB86-59B4-43C3-A9DB-9B499DD8FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF8FE9-0D44-F646-80B7-16AE6F250B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8736" yWindow="7140" windowWidth="34560" windowHeight="18600" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="38400" windowHeight="22960" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="units_frequencyparam" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>index</t>
   </si>
@@ -201,17 +201,20 @@
   <si>
     <t>sv_constant</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gens_t1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -230,18 +233,31 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -274,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -294,14 +310,41 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -367,9 +410,9 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="表6" displayName="表6" ref="A1:M4" totalsRowShown="0">
-  <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="表6" displayName="表6" ref="A1:N4" totalsRowShown="0">
+  <autoFilter ref="A1:N4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="index"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="locate_bus"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="p_max"/>
@@ -383,6 +426,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Gens_x0"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="Gens_t0"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Gens_p0"/>
+    <tableColumn id="14" xr3:uid="{EF870B2E-34C2-234E-BE9A-84EC291628D6}" name="Gens_t1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -420,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="表11" displayName="表11" ref="A1:B25" totalsRowShown="0">
-  <autoFilter ref="A1:B25" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="表11" displayName="表11" ref="A1:B169" totalsRowShown="0">
+  <autoFilter ref="A1:B169" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="index"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="p"/>
@@ -731,18 +775,18 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,7 +809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -788,7 +832,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -811,7 +855,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -849,14 +893,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -876,7 +920,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -896,7 +940,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -931,20 +975,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +1026,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1034,20 +1078,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1087,8 +1131,11 @@
       <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1128,8 +1175,11 @@
       <c r="M2" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1169,8 +1219,11 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1209,11 +1262,15 @@
       </c>
       <c r="M4" s="1">
         <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1226,16 +1283,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1287,7 +1344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1313,7 +1370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>6</v>
       </c>
@@ -1354,15 +1411,15 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1396,7 +1453,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1413,7 +1470,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1430,7 +1487,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1447,7 +1504,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1464,7 +1521,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1481,7 +1538,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1512,14 +1569,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B169"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1535,7 +1592,7 @@
         <v>219.19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1543,7 +1600,7 @@
         <v>235.35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1551,7 +1608,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1559,7 +1616,7 @@
         <v>236.73</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1567,7 +1624,7 @@
         <v>239.06</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1575,7 +1632,7 @@
         <v>244.48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1583,7 +1640,7 @@
         <v>273.39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1591,7 +1648,7 @@
         <v>290.39999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1599,7 +1656,7 @@
         <v>283.56</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1607,7 +1664,7 @@
         <v>281.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1615,7 +1672,7 @@
         <v>328.61</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1623,7 +1680,7 @@
         <v>328.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1631,7 +1688,7 @@
         <v>326.18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1639,7 +1696,7 @@
         <v>323.60000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1647,7 +1704,7 @@
         <v>326.86</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1655,7 +1712,7 @@
         <v>287.79000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1663,7 +1720,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1671,7 +1728,7 @@
         <v>246.74</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1679,7 +1736,7 @@
         <v>255.97</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1687,7 +1744,7 @@
         <v>237.35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1695,7 +1752,7 @@
         <v>243.31</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1703,7 +1760,7 @@
         <v>283.14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1711,17 +1768,1170 @@
         <v>283.05</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="7">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="7">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="7">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="7">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="7">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="7">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="8">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="7">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="8">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="7">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="8">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="7">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="8">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="7">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="8">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="7">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="8">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="7">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="8">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="7">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="8">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="7">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="8">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="7">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="8">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="7">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="8">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="7">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="8">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="7">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="8">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="8">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="7">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="8">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="7">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="8">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="7">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="8">
+        <v>248.75</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="7">
+        <v>219.19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="8">
+        <v>235.35</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="7">
+        <v>234.67</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="8">
+        <v>236.73</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="7">
+        <v>239.06</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="8">
+        <v>244.48</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="7">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="8">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="7">
+        <v>283.56</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="8">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="7">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="8">
+        <v>328.1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="7">
+        <v>326.18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="8">
+        <v>323.60000000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="7">
+        <v>326.86</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="8">
+        <v>287.79000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="8">
+        <v>246.74</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="7">
+        <v>255.97</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="8">
+        <v>237.35</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="7">
+        <v>243.31</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="8">
+        <v>283.14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="7">
+        <v>283.05</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="8">
         <v>248.75</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1734,14 +2944,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1752,7 +2962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1763,7 +2973,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1774,7 +2984,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1797,15 +3007,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE2AA48-EAC4-44C8-A371-1C9C338278CF}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1821,10 +3031,10 @@
       <c r="E1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H1" s="6" t="s">
@@ -1834,7 +3044,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1863,7 +3073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1892,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1921,7 +3131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1950,7 +3160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1979,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2008,7 +3218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2037,7 +3247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyiping/Documents/GitHub/module_unitcommitment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF8FE9-0D44-F646-80B7-16AE6F250B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1C7959-9A31-3247-A5A2-ED4CCD76CDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="38400" windowHeight="22960" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1460" windowWidth="38400" windowHeight="21100" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="units_frequencyparam" sheetId="1" r:id="rId1"/>
@@ -22,13 +22,28 @@
     <sheet name="load_curve" sheetId="7" r:id="rId7"/>
     <sheet name="load_data" sheetId="8" r:id="rId8"/>
     <sheet name="data_centra" sheetId="9" r:id="rId9"/>
+    <sheet name="hydro_data" sheetId="10" r:id="rId10"/>
+    <sheet name="hydro_seasoncurve" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
   <si>
     <t>index</t>
   </si>
@@ -204,6 +219,15 @@
   </si>
   <si>
     <t>Gens_t1</t>
+  </si>
+  <si>
+    <t>qmax</t>
+  </si>
+  <si>
+    <t>q0</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -290,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -319,11 +343,32 @@
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -368,6 +413,17 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Fg(0.15,0.4)"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Tg(6,14)"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rg(0.04,0.1)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{90DA1D3D-F6FB-2945-BBFB-035702378813}" name="表11_10" displayName="表11_10" ref="A1:B169" totalsRowShown="0">
+  <autoFilter ref="A1:B169" xr:uid="{90DA1D3D-F6FB-2945-BBFB-035702378813}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{CFC9E3BB-3CBD-2B49-987D-49950F1CF078}" name="index"/>
+    <tableColumn id="2" xr3:uid="{5CFC1256-5DCA-0343-804E-77C92C9A264A}" name="p"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -426,7 +482,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Gens_x0"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="Gens_t0"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Gens_p0"/>
-    <tableColumn id="14" xr3:uid="{EF870B2E-34C2-234E-BE9A-84EC291628D6}" name="Gens_t1" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{EF870B2E-34C2-234E-BE9A-84EC291628D6}" name="Gens_t1" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -483,6 +539,21 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A802B22F-A946-6145-BB93-E071DBF84974}" name="Table10" displayName="Table10" ref="A1:F9" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F9" xr:uid="{A802B22F-A946-6145-BB93-E071DBF84974}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{2C34CE5F-8262-7546-9A26-C746718FA026}" name="index"/>
+    <tableColumn id="2" xr3:uid="{1FC8BCD2-C02B-C740-BBC8-19CD824FD767}" name="locatebus"/>
+    <tableColumn id="3" xr3:uid="{8041F6BD-D058-4640-B99B-739BF9B6FA31}" name="p_max"/>
+    <tableColumn id="4" xr3:uid="{DEA14585-2788-FB43-9A3D-C768216ECB72}" name="p_min"/>
+    <tableColumn id="5" xr3:uid="{48E370AE-D3AF-E64F-8116-3DD9FA90D2B9}" name="qmax"/>
+    <tableColumn id="6" xr3:uid="{F43521CB-B297-864B-9BC3-CB246032D773}" name="q0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -887,6 +958,1578 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA492298-718A-294F-AA8A-B9EF8645097E}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="10.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>0.1</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>0.1</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FDC3B1-AAE8-EB49-94CD-DAD9D4E18BE9}">
+  <dimension ref="A1:N169"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2.4110899999999997</v>
+      </c>
+      <c r="N26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="7">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="7">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="7">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="7">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="7">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="7">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="7">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="7">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="7">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="7">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="7">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="7">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="7">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="8">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="7">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="8">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="7">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="8">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="8">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="7">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="8">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="7">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="8">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="7">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="8">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="7">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="8">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="7">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="8">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="7">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="8">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="7">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="8">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="7">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="8">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="7">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="8">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="7">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="8">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="7">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="8">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="8">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="7">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="8">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="7">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="8">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="7">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="8">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="7">
+        <v>2.4110899999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="8">
+        <v>2.5888499999999999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="7">
+        <v>2.5813699999999997</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="8">
+        <v>2.6040299999999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="7">
+        <v>2.6296599999999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="8">
+        <v>2.6892799999999997</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="7">
+        <v>3.0072899999999998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="8">
+        <v>3.1943999999999995</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="7">
+        <v>3.1191599999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="8">
+        <v>3.0931999999999995</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="7">
+        <v>3.6147100000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="8">
+        <v>3.6091000000000002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="7">
+        <v>3.5879799999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="8">
+        <v>3.5596000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="7">
+        <v>3.5954600000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="8">
+        <v>3.1656900000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="9">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="8">
+        <v>2.71414</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="7">
+        <v>2.8156699999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="8">
+        <v>2.6108499999999997</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="7">
+        <v>2.6764099999999997</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="8">
+        <v>3.1145399999999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="7">
+        <v>3.11355</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="8">
+        <v>2.7362499999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
@@ -3279,5 +4922,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,60 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyiping/Documents/GitHub/module_unitcommitment/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1C7959-9A31-3247-A5A2-ED4CCD76CDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1460" windowWidth="38400" windowHeight="21100" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
-    <sheet name="units_frequencyparam" sheetId="1" r:id="rId1"/>
-    <sheet name="winds_frequencyparam" sheetId="2" r:id="rId2"/>
-    <sheet name="strogesystem_data" sheetId="3" r:id="rId3"/>
-    <sheet name="units_data" sheetId="4" r:id="rId4"/>
-    <sheet name="units_cost" sheetId="5" r:id="rId5"/>
-    <sheet name="branch_data" sheetId="6" r:id="rId6"/>
-    <sheet name="load_curve" sheetId="7" r:id="rId7"/>
-    <sheet name="load_data" sheetId="8" r:id="rId8"/>
-    <sheet name="data_centra" sheetId="9" r:id="rId9"/>
-    <sheet name="hydro_data" sheetId="10" r:id="rId10"/>
-    <sheet name="hydro_seasoncurve" sheetId="11" r:id="rId11"/>
+    <sheet r:id="rId1" sheetId="1" name="units_frequencyparam"/>
+    <sheet r:id="rId2" sheetId="2" name="winds_frequencyparam"/>
+    <sheet r:id="rId3" sheetId="3" name="strogesystem_data"/>
+    <sheet r:id="rId4" sheetId="4" name="units_data"/>
+    <sheet r:id="rId5" sheetId="5" name="units_cost"/>
+    <sheet r:id="rId6" sheetId="6" name="branch_data"/>
+    <sheet r:id="rId7" sheetId="7" name="load_curve"/>
+    <sheet r:id="rId8" sheetId="8" name="load_data"/>
+    <sheet r:id="rId9" sheetId="9" name="data_centra"/>
+    <sheet r:id="rId10" sheetId="10" name="hydro_data"/>
+    <sheet r:id="rId11" sheetId="11" name="hydro_seasoncurve"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
   <si>
     <t>index</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>locatebus</t>
+  </si>
+  <si>
+    <t>p_max</t>
+  </si>
+  <si>
+    <t>p_min</t>
+  </si>
+  <si>
+    <t>qmax</t>
+  </si>
+  <si>
+    <t>q0</t>
+  </si>
+  <si>
+    <t>voltage_regulation</t>
+  </si>
+  <si>
+    <t>idale</t>
+  </si>
+  <si>
+    <t>sv_constant</t>
+  </si>
+  <si>
+    <t>lambda</t>
+  </si>
+  <si>
+    <t>mu</t>
   </si>
   <si>
     <t>locate_bus</t>
   </si>
   <si>
     <t>percent</t>
-  </si>
-  <si>
-    <t>p</t>
   </si>
   <si>
     <t>from</t>
@@ -64,9 +81,6 @@
   </si>
   <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>p_max</t>
   </si>
   <si>
     <t>Gens_c</t>
@@ -88,9 +102,6 @@
   </si>
   <si>
     <t>Gens_Cold</t>
-  </si>
-  <si>
-    <t>p_min</t>
   </si>
   <si>
     <t>Gens_RD</t>
@@ -118,6 +129,9 @@
   </si>
   <si>
     <t>Gens_p0</t>
+  </si>
+  <si>
+    <t>Gens_t1</t>
   </si>
   <si>
     <t>q_max</t>
@@ -185,56 +199,13 @@
   <si>
     <t>Rg(0.04,0.1)</t>
   </si>
-  <si>
-    <t>p_max</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>p_min</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>locatebus</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>voltage_regulation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>lambda</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mu</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>idale</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>sv_constant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gens_t1</t>
-  </si>
-  <si>
-    <t>qmax</t>
-  </si>
-  <si>
-    <t>q0</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,18 +227,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -279,12 +242,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFd9d9d9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -300,13 +262,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -314,246 +291,216 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表5" displayName="表5" ref="A1:G4" totalsRowShown="0">
-  <autoFilter ref="A1:G4" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hg(3,9)"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dg(0,0.02)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Kg(0,1)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Fg(0.15,0.4)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Tg(6,14)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Rg(0.04,0.1)"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B169" displayName="表11_10" name="表11_10" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:B169"/>
+  <tableColumns count="2">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="p" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{90DA1D3D-F6FB-2945-BBFB-035702378813}" name="表11_10" displayName="表11_10" ref="A1:B169" totalsRowShown="0">
-  <autoFilter ref="A1:B169" xr:uid="{90DA1D3D-F6FB-2945-BBFB-035702378813}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CFC9E3BB-3CBD-2B49-987D-49950F1CF078}" name="index"/>
-    <tableColumn id="2" xr3:uid="{5CFC1256-5DCA-0343-804E-77C92C9A264A}" name="p"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G4" displayName="表5" name="表5" id="10" totalsRowShown="0">
+  <autoFilter ref="A1:G4"/>
+  <tableColumns count="7">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="Hg(3,9)" id="2"/>
+    <tableColumn name="Dg(0,0.02)" id="3"/>
+    <tableColumn name="Kg(0,1)" id="4"/>
+    <tableColumn name="Fg(0.15,0.4)" id="5"/>
+    <tableColumn name="Tg(6,14)" id="6"/>
+    <tableColumn name="Rg(0.04,0.1)" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="表2" displayName="表2" ref="A1:F3" totalsRowShown="0">
-  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F9" displayName="Table10" name="Table10" id="2" totalsRowShown="0">
+  <autoFilter ref="A1:F9"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fcmodel"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Kw"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Rw"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Mw"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Dw"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Tw"/>
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="locatebus" id="2"/>
+    <tableColumn name="p_max" id="3"/>
+    <tableColumn name="p_min" id="4"/>
+    <tableColumn name="qmax" id="5"/>
+    <tableColumn name="q0" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="表3" displayName="表3" ref="A1:L2" totalsRowShown="0">
-  <autoFilter ref="A1:L2" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="locate_bus"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="q_max"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="q_min"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="pg_max"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="pd_min"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="p_0"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="charge_rate"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="discharge_rate"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="charge_effi"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="discharge_effi"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="lossing_effi"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C4" displayName="表12" name="表12" id="3" totalsRowShown="0">
+  <autoFilter ref="A1:C4"/>
+  <tableColumns count="3">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="locate_bus" id="2"/>
+    <tableColumn name="percent" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="表6" displayName="表6" ref="A1:N4" totalsRowShown="0">
-  <autoFilter ref="A1:N4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="locate_bus"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="p_max"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="p_min"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Gens_RD"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Gens_RU"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Gens_SD"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Gens_SU"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Gens_TU"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Gens_TD"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Gens_x0"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="Gens_t0"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Gens_p0"/>
-    <tableColumn id="14" xr3:uid="{EF870B2E-34C2-234E-BE9A-84EC291628D6}" name="Gens_t1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:B169" displayName="表11" name="表11" id="4" totalsRowShown="0">
+  <autoFilter ref="A1:B169"/>
+  <tableColumns count="2">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="p" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="表7" displayName="表7" ref="A1:H4" totalsRowShown="0">
-  <autoFilter ref="A1:H4" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Gens_c"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Gens_b"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Gens_a"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Gens_CD"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Gens_CU"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Gens_CU1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Gens_Cold"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E8" displayName="表10" name="表10" id="5" totalsRowShown="0">
+  <autoFilter ref="A1:E8"/>
+  <tableColumns count="5">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="from" id="2"/>
+    <tableColumn name="to" id="3"/>
+    <tableColumn name="x" id="4"/>
+    <tableColumn name="p_max" id="5"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="表10" displayName="表10" ref="A1:E8" totalsRowShown="0">
-  <autoFilter ref="A1:E8" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="from"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="to"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="x"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="p_max"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H4" displayName="表7" name="表7" id="6" totalsRowShown="0">
+  <autoFilter ref="A1:H4"/>
+  <tableColumns count="8">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="Gens_c" id="2"/>
+    <tableColumn name="Gens_b" id="3"/>
+    <tableColumn name="Gens_a" id="4"/>
+    <tableColumn name="Gens_CD" id="5"/>
+    <tableColumn name="Gens_CU" id="6"/>
+    <tableColumn name="Gens_CU1" id="7"/>
+    <tableColumn name="Gens_Cold" id="8"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="表11" displayName="表11" ref="A1:B169" totalsRowShown="0">
-  <autoFilter ref="A1:B169" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="p"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N4" displayName="表6" name="表6" id="7" totalsRowShown="0">
+  <autoFilter ref="A1:N4"/>
+  <tableColumns count="14">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="locate_bus" id="2"/>
+    <tableColumn name="p_max" id="3"/>
+    <tableColumn name="p_min" id="4"/>
+    <tableColumn name="Gens_RD" id="5"/>
+    <tableColumn name="Gens_RU" id="6"/>
+    <tableColumn name="Gens_SD" id="7"/>
+    <tableColumn name="Gens_SU" id="8"/>
+    <tableColumn name="Gens_TU" id="9"/>
+    <tableColumn name="Gens_TD" id="10"/>
+    <tableColumn name="Gens_x0" id="11"/>
+    <tableColumn name="Gens_t0" id="12"/>
+    <tableColumn name="Gens_p0" id="13"/>
+    <tableColumn name="Gens_t1" id="14"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="表12" displayName="表12" ref="A1:C4" totalsRowShown="0">
-  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="index"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="locate_bus"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="percent"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L2" displayName="表3" name="表3" id="8" totalsRowShown="0">
+  <autoFilter ref="A1:L2"/>
+  <tableColumns count="12">
+    <tableColumn name="index" id="1"/>
+    <tableColumn name="locate_bus" id="2"/>
+    <tableColumn name="q_max" id="3"/>
+    <tableColumn name="q_min" id="4"/>
+    <tableColumn name="pg_max" id="5"/>
+    <tableColumn name="pd_min" id="6"/>
+    <tableColumn name="p_0" id="7"/>
+    <tableColumn name="charge_rate" id="8"/>
+    <tableColumn name="discharge_rate" id="9"/>
+    <tableColumn name="charge_effi" id="10"/>
+    <tableColumn name="discharge_effi" id="11"/>
+    <tableColumn name="lossing_effi" id="12"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A802B22F-A946-6145-BB93-E071DBF84974}" name="Table10" displayName="Table10" ref="A1:F9" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F9" xr:uid="{A802B22F-A946-6145-BB93-E071DBF84974}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F3" displayName="表2" name="表2" id="9" totalsRowShown="0">
+  <autoFilter ref="A1:F3"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2C34CE5F-8262-7546-9A26-C746718FA026}" name="index"/>
-    <tableColumn id="2" xr3:uid="{1FC8BCD2-C02B-C740-BBC8-19CD824FD767}" name="locatebus"/>
-    <tableColumn id="3" xr3:uid="{8041F6BD-D058-4640-B99B-739BF9B6FA31}" name="p_max"/>
-    <tableColumn id="4" xr3:uid="{DEA14585-2788-FB43-9A3D-C768216ECB72}" name="p_min"/>
-    <tableColumn id="5" xr3:uid="{48E370AE-D3AF-E64F-8116-3DD9FA90D2B9}" name="qmax"/>
-    <tableColumn id="6" xr3:uid="{F43521CB-B297-864B-9BC3-CB246032D773}" name="q0"/>
+    <tableColumn name="Fcmodel" id="1"/>
+    <tableColumn name="Kw" id="2"/>
+    <tableColumn name="Rw" id="3"/>
+    <tableColumn name="Mw" id="4"/>
+    <tableColumn name="Dw" id="5"/>
+    <tableColumn name="Tw" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="0" showFirstColumn="0"/>
 </table>
 </file>
 
@@ -562,10 +509,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -603,71 +550,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -695,7 +642,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -718,11 +665,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -731,13 +678,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -747,7 +694,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -756,7 +703,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -765,7 +712,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -773,10 +720,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -841,46 +788,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="8.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="9.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="12.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -888,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="D2" s="2">
         <v>0.9</v>
@@ -903,7 +850,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -926,7 +873,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -934,7 +881,7 @@
         <v>3.5</v>
       </c>
       <c r="C4" s="2">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="D4" s="2">
         <v>0.98</v>
@@ -950,7 +897,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -959,192 +905,198 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA492298-718A-294F-AA8A-B9EF8645097E}">
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="10.83203125" style="10"/>
+    <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="10.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="B1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="13">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="14">
         <v>0.1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="13">
         <v>50</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="13">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="13">
         <v>5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="14">
         <v>0.1</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="13">
         <v>50</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="13">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="14">
         <v>0.1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="13">
         <v>50</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="13">
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="14">
         <v>0.1</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="13">
         <v>50</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="13">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="13">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="14">
         <v>0.1</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="13">
         <v>50</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="13">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="13">
         <v>5</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="14">
         <v>0.1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="13">
         <v>50</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="13">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="13">
         <v>5</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="14">
         <v>0.1</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="13">
         <v>50</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="13">
         <v>1</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="13">
         <v>5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="14">
         <v>0.1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="13">
         <v>50</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="14">
         <v>0.5</v>
       </c>
     </row>
@@ -1157,1373 +1109,3415 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FDC3B1-AAE8-EB49-94CD-DAD9D4E18BE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:N169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2.58885</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2.60403</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2.62966</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.00729</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.11916</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.61471</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.6091</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.58798</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.5596</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3.59546</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3.16569</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2.81567</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3.11454</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>2.4110899999999997</v>
       </c>
-      <c r="N26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2.58885</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2.60403</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+        <v>2.62966</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.00729</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.11916</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.61471</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.6091</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.58798</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.5596</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.59546</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.16569</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2.81567</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="2">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3.11454</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="2">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="4">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="8">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="2">
+        <v>2.58885</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="4">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="8">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="2">
+        <v>2.60403</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="7">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="4">
+        <v>2.62966</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="7">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="4">
+        <v>3.00729</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="7">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B58" s="4">
+        <v>3.11916</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="7">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B60" s="4">
+        <v>3.61471</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="8">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B61" s="2">
+        <v>3.6091</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="7">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B62" s="4">
+        <v>3.58798</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="8">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B63" s="2">
+        <v>3.5596</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="7">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B64" s="4">
+        <v>3.59546</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="8">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="2">
+        <v>3.16569</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="5">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="7">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B68" s="4">
+        <v>2.81567</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="4">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="8">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B71" s="2">
+        <v>3.11454</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="4">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="4">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="8">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B75" s="2">
+        <v>2.58885</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="4">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="8">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B77" s="2">
+        <v>2.60403</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="7">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B78" s="4">
+        <v>2.62966</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="7">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B80" s="4">
+        <v>3.00729</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="7">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B82" s="4">
+        <v>3.11916</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="7">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B84" s="4">
+        <v>3.61471</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="8">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B85" s="2">
+        <v>3.6091</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="7">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B86" s="4">
+        <v>3.58798</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="8">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B87" s="2">
+        <v>3.5596</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="7">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B88" s="4">
+        <v>3.59546</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="8">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B89" s="2">
+        <v>3.16569</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="5">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="7">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B92" s="4">
+        <v>2.81567</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="4">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="8">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B95" s="2">
+        <v>3.11454</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="4">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="4">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="8">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B99" s="2">
+        <v>2.58885</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="4">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="8">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B101" s="2">
+        <v>2.60403</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="B102" s="7">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B102" s="4">
+        <v>2.62966</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="B104" s="7">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B104" s="4">
+        <v>3.00729</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="B106" s="7">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B106" s="4">
+        <v>3.11916</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="B108" s="7">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="4">
+        <v>3.61471</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="B109" s="8">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="2">
+        <v>3.6091</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="B110" s="7">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="4">
+        <v>3.58798</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="B111" s="8">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="2">
+        <v>3.5596</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="B112" s="7">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="4">
+        <v>3.59546</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B113" s="8">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="2">
+        <v>3.16569</v>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="5">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="7">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="4">
+        <v>2.81567</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="4">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="B119" s="8">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="2">
+        <v>3.11454</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="4">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="4">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="B123" s="8">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="2">
+        <v>2.58885</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="4">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="B125" s="8">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="2">
+        <v>2.60403</v>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="B126" s="7">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="4">
+        <v>2.62966</v>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="B128" s="7">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="4">
+        <v>3.00729</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="3"/>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="B130" s="7">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="4">
+        <v>3.11916</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="7">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="4">
+        <v>3.61471</v>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="B133" s="8">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="2">
+        <v>3.6091</v>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="B134" s="7">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="4">
+        <v>3.58798</v>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="B135" s="8">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="2">
+        <v>3.5596</v>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="3"/>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="B136" s="7">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="4">
+        <v>3.59546</v>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="3"/>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="B137" s="8">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="2">
+        <v>3.16569</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="5">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="B140" s="7">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="4">
+        <v>2.81567</v>
+      </c>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="4">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="B143" s="8">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="2">
+        <v>3.11454</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="4">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="2">
         <v>2.7362499999999996</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3"/>
+      <c r="L145" s="3"/>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="4">
         <v>2.4110899999999997</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
+      <c r="L146" s="3"/>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="8">
-        <v>2.5888499999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="2">
+        <v>2.58885</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="4">
         <v>2.5813699999999997</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="3"/>
+      <c r="K148" s="3"/>
+      <c r="L148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="B149" s="8">
-        <v>2.6040299999999998</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="2">
+        <v>2.60403</v>
+      </c>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3"/>
+      <c r="K149" s="3"/>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="B150" s="7">
-        <v>2.6296599999999999</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="4">
+        <v>2.62966</v>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+      <c r="L150" s="3"/>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="2">
         <v>2.6892799999999997</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="B152" s="7">
-        <v>3.0072899999999998</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="4">
+        <v>3.00729</v>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="3"/>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="2">
         <v>3.1943999999999995</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="3"/>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="B154" s="7">
-        <v>3.1191599999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="4">
+        <v>3.11916</v>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="3"/>
+      <c r="K154" s="3"/>
+      <c r="L154" s="3"/>
+      <c r="M154" s="3"/>
+      <c r="N154" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B155" s="2">
         <v>3.0931999999999995</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="3"/>
+      <c r="M155" s="3"/>
+      <c r="N155" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="7">
-        <v>3.6147100000000001</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="4">
+        <v>3.61471</v>
+      </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3"/>
+      <c r="K156" s="3"/>
+      <c r="L156" s="3"/>
+      <c r="M156" s="3"/>
+      <c r="N156" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="B157" s="8">
-        <v>3.6091000000000002</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="2">
+        <v>3.6091</v>
+      </c>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3"/>
+      <c r="N157" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="B158" s="7">
-        <v>3.5879799999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="4">
+        <v>3.58798</v>
+      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3"/>
+      <c r="L158" s="3"/>
+      <c r="M158" s="3"/>
+      <c r="N158" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="B159" s="8">
-        <v>3.5596000000000001</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="2">
+        <v>3.5596</v>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="3"/>
+      <c r="K159" s="3"/>
+      <c r="L159" s="3"/>
+      <c r="M159" s="3"/>
+      <c r="N159" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="7">
-        <v>3.5954600000000001</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="4">
+        <v>3.59546</v>
+      </c>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="3"/>
+      <c r="L160" s="3"/>
+      <c r="M160" s="3"/>
+      <c r="N160" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="B161" s="8">
-        <v>3.1656900000000001</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="2">
+        <v>3.16569</v>
+      </c>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="3"/>
+      <c r="K161" s="3"/>
+      <c r="L161" s="3"/>
+      <c r="M161" s="3"/>
+      <c r="N161" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="5">
         <v>2.86</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="3"/>
+      <c r="M162" s="3"/>
+      <c r="N162" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B163" s="2">
         <v>2.71414</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="3"/>
+      <c r="K163" s="3"/>
+      <c r="L163" s="3"/>
+      <c r="M163" s="3"/>
+      <c r="N163" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="B164" s="7">
-        <v>2.8156699999999999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="4">
+        <v>2.81567</v>
+      </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="3"/>
+      <c r="M164" s="3"/>
+      <c r="N164" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B165" s="2">
         <v>2.6108499999999997</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="3"/>
+      <c r="M165" s="3"/>
+      <c r="N165" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="4">
         <v>2.6764099999999997</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+      <c r="N166" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="B167" s="8">
-        <v>3.1145399999999999</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="2">
+        <v>3.11454</v>
+      </c>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+      <c r="N167" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="4">
         <v>3.11355</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="3"/>
+      <c r="N168" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B169" s="2">
         <v>2.7362499999999996</v>
       </c>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="3"/>
+      <c r="M169" s="3"/>
+      <c r="N169" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2531,39 +4525,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -2571,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -2583,7 +4580,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2597,14 +4594,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="2">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="F3" s="2">
         <v>0.06</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2613,63 +4609,66 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="6.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="6" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2708,7 +4707,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2717,68 +4715,74 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="6" width="9.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="6" width="9.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="6" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="6" width="9.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2822,7 +4826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2866,7 +4870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2911,9 +4915,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -2921,47 +4923,50 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="9.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="11.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2972,7 +4977,7 @@
         <v>13.5</v>
       </c>
       <c r="D2" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>0.0004</v>
       </c>
       <c r="E2" s="1">
         <v>560</v>
@@ -2987,7 +4992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2998,7 +5003,7 @@
         <v>32.6</v>
       </c>
       <c r="D3" s="2">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="E3" s="1">
         <v>350</v>
@@ -3013,7 +5018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>6</v>
       </c>
@@ -3021,10 +5026,10 @@
         <v>137.4</v>
       </c>
       <c r="C4" s="2">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="D4" s="2">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="E4" s="1">
         <v>260</v>
@@ -3040,7 +5045,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3049,37 +5053,38 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="8.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3096,7 +5101,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3107,13 +5112,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="2">
-        <v>0.25800000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="E3" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3124,13 +5129,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="2">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="E4" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3141,13 +5146,13 @@
         <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E5" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3158,13 +5163,13 @@
         <v>6</v>
       </c>
       <c r="D6" s="2">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="E6" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3175,13 +5180,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="E7" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3192,14 +5197,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="2">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="E8" s="1">
         <v>120</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3208,26 +5212,26 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B169"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3235,7 +5239,7 @@
         <v>219.19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3243,7 +5247,7 @@
         <v>235.35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3251,7 +5255,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3259,7 +5263,7 @@
         <v>236.73</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3267,7 +5271,7 @@
         <v>239.06</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3275,7 +5279,7 @@
         <v>244.48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3283,15 +5287,15 @@
         <v>273.39</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3299,7 +5303,7 @@
         <v>283.56</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3307,7 +5311,7 @@
         <v>281.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3315,7 +5319,7 @@
         <v>328.61</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3323,7 +5327,7 @@
         <v>328.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3331,15 +5335,15 @@
         <v>326.18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3347,15 +5351,15 @@
         <v>326.86</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3363,7 +5367,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3371,7 +5375,7 @@
         <v>246.74</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3379,7 +5383,7 @@
         <v>255.97</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3387,7 +5391,7 @@
         <v>237.35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3395,7 +5399,7 @@
         <v>243.31</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3403,7 +5407,7 @@
         <v>283.14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3411,7 +5415,7 @@
         <v>283.05</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3419,7 +5423,7 @@
         <v>248.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3427,7 +5431,7 @@
         <v>219.19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3435,7 +5439,7 @@
         <v>235.35</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3443,7 +5447,7 @@
         <v>234.67</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3451,7 +5455,7 @@
         <v>236.73</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3459,7 +5463,7 @@
         <v>239.06</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3467,7 +5471,7 @@
         <v>244.48</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3475,15 +5479,15 @@
         <v>273.39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3491,7 +5495,7 @@
         <v>283.56</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3499,7 +5503,7 @@
         <v>281.2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3507,7 +5511,7 @@
         <v>328.61</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3515,7 +5519,7 @@
         <v>328.1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3523,15 +5527,15 @@
         <v>326.18</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3539,15 +5543,15 @@
         <v>326.86</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3555,7 +5559,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3563,7 +5567,7 @@
         <v>246.74</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3571,7 +5575,7 @@
         <v>255.97</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3579,7 +5583,7 @@
         <v>237.35</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3587,7 +5591,7 @@
         <v>243.31</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3595,7 +5599,7 @@
         <v>283.14</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3603,7 +5607,7 @@
         <v>283.05</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3611,970 +5615,968 @@
         <v>248.75</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="4">
         <v>219.19</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="2">
         <v>235.35</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="4">
         <v>234.67</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="2">
         <v>236.73</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="4">
         <v>239.06</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="2">
         <v>244.48</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="4">
         <v>273.39</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="8">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="4">
         <v>283.56</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="2">
         <v>281.2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="4">
         <v>328.61</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="2">
         <v>328.1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="4">
         <v>326.18</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="8">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B63" s="2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="4">
         <v>326.86</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="8">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="5">
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="2">
         <v>246.74</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="4">
         <v>255.97</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="2">
         <v>237.35</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="4">
         <v>243.31</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="2">
         <v>283.14</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="4">
         <v>283.05</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="2">
         <v>248.75</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="4">
         <v>219.19</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="2">
         <v>235.35</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="4">
         <v>234.67</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="2">
         <v>236.73</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="4">
         <v>239.06</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="2">
         <v>244.48</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="4">
         <v>273.39</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="8">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B81" s="2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="4">
         <v>283.56</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="2">
         <v>281.2</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="4">
         <v>328.61</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="2">
         <v>328.1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="4">
         <v>326.18</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="8">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B87" s="2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="4">
         <v>326.86</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="8">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B89" s="2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="5">
         <v>260</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="2">
         <v>246.74</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="4">
         <v>255.97</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="2">
         <v>237.35</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="4">
         <v>243.31</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="2">
         <v>283.14</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="4">
         <v>283.05</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="2">
         <v>248.75</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="4">
         <v>219.19</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="2">
         <v>235.35</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="4">
         <v>234.67</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="2">
         <v>236.73</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="4">
         <v>239.06</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="2">
         <v>244.48</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="4">
         <v>273.39</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="B105" s="8">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B105" s="2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="4">
         <v>283.56</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="2">
         <v>281.2</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="4">
         <v>328.61</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="2">
         <v>328.1</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="4">
         <v>326.18</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="B111" s="8">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="4">
         <v>326.86</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B113" s="8">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="5">
         <v>260</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="2">
         <v>246.74</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="4">
         <v>255.97</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="2">
         <v>237.35</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="4">
         <v>243.31</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="2">
         <v>283.14</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="4">
         <v>283.05</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="2">
         <v>248.75</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="4">
         <v>219.19</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="2">
         <v>235.35</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="4">
         <v>234.67</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="2">
         <v>236.73</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="4">
         <v>239.06</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="2">
         <v>244.48</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="4">
         <v>273.39</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="B129" s="8">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="4">
         <v>283.56</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="2">
         <v>281.2</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="4">
         <v>328.61</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="2">
         <v>328.1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="4">
         <v>326.18</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="B135" s="8">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="4">
         <v>326.86</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="B137" s="8">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="5">
         <v>260</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="2">
         <v>246.74</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="4">
         <v>255.97</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="2">
         <v>237.35</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="4">
         <v>243.31</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="B143" s="8">
+      <c r="B143" s="2">
         <v>283.14</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="4">
         <v>283.05</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="2">
         <v>248.75</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="4">
         <v>219.19</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="2">
         <v>235.35</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="4">
         <v>234.67</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="2">
         <v>236.73</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="4">
         <v>239.06</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="2">
         <v>244.48</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="4">
         <v>273.39</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="B153" s="8">
-        <v>290.39999999999998</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="2">
+        <v>290.4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="4">
         <v>283.56</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B155" s="2">
         <v>281.2</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156" s="4">
         <v>328.61</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="B157" s="8">
+      <c r="B157" s="2">
         <v>328.1</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="4">
         <v>326.18</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="B159" s="8">
-        <v>323.60000000000002</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="2">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="4">
         <v>326.86</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="B161" s="8">
-        <v>287.79000000000002</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="2">
+        <v>287.79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="5">
         <v>260</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B163" s="2">
         <v>246.74</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="4">
         <v>255.97</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B165" s="2">
         <v>237.35</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="4">
         <v>243.31</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="B167" s="8">
+      <c r="B167" s="2">
         <v>283.14</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="4">
         <v>283.05</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B169" s="2">
         <v>248.75</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -4582,30 +6584,30 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4616,7 +6618,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4627,7 +6629,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4639,7 +6641,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -4648,280 +6649,286 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE2AA48-EAC4-44C8-A371-1C9C338278CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="1" max="1" style="6" width="7.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="19.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="B1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="13">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="14">
         <v>0.5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="14">
         <v>0.1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="13">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="14">
         <v>0.05</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="14">
         <v>0.3</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="14">
         <v>0.5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="13">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="14">
         <v>0.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="14">
         <v>0.1</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="14">
         <v>0.05</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="14">
         <v>0.3</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="14">
         <v>0.2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="14">
         <v>0.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="14">
         <v>0.1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="13">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="14">
         <v>0.05</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="14">
         <v>0.3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="14">
         <v>0.1</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="14">
         <v>0.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="14">
         <v>0.1</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="13">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="14">
         <v>0.05</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="14">
         <v>0.3</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="14">
         <v>0.3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="13">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="14">
         <v>0.5</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="14">
         <v>0.1</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="13">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="14">
         <v>0.05</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="14">
         <v>0.3</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="14">
         <v>0.4</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="13">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="14">
         <v>0.5</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="14">
         <v>0.1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="13">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="14">
         <v>0.05</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="14">
         <v>0.3</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="14">
         <v>0.4</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="13">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="14">
         <v>0.5</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="14">
         <v>0.1</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="13">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="14">
         <v>0.05</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="14">
         <v>0.3</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="14">
         <v>0.5</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="13">
         <v>1</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="14">
         <v>0.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="14">
         <v>0.1</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="13">
         <v>1</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="14">
         <v>0.05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="14">
         <v>0.3</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="14">
         <v>0.2</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="13">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>